--- a/data/candidatures-gala-2027.xlsx
+++ b/data/candidatures-gala-2027.xlsx
@@ -1,49 +1,124 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25000" windowHeight="10000" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Candidatures" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Documents" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet sheetId="1" name="Candidatures" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Documents" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Candidatures'!$A$1:$T$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Documents'!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase">Documents!$A$1:$F$1</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
+  <si>
+    <t>Référence</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Langue</t>
+  </si>
+  <si>
+    <t>Prix</t>
+  </si>
+  <si>
+    <t>Nom</t>
+  </si>
+  <si>
+    <t>Organisation</t>
+  </si>
+  <si>
+    <t>Ville</t>
+  </si>
+  <si>
+    <t>Courriel</t>
+  </si>
+  <si>
+    <t>Téléphone</t>
+  </si>
+  <si>
+    <t>Lien</t>
+  </si>
+  <si>
+    <t>Âge</t>
+  </si>
+  <si>
+    <t>Déposé par</t>
+  </si>
+  <si>
+    <t>Nom proposant</t>
+  </si>
+  <si>
+    <t>Courriel proposant</t>
+  </si>
+  <si>
+    <t>Parcours</t>
+  </si>
+  <si>
+    <t>Racines</t>
+  </si>
+  <si>
+    <t>Audace</t>
+  </si>
+  <si>
+    <t>Liens supplémentaires</t>
+  </si>
+  <si>
+    <t>Références</t>
+  </si>
+  <si>
+    <t>Documents</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Taille</t>
+  </si>
+  <si>
+    <t>Chemin GitHub</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill/>
     </fill>
   </fills>
   <borders count="1">
@@ -59,81 +134,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -421,136 +437,91 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:T1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="45" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="28" customWidth="1" min="13" max="13"/>
-    <col width="30" customWidth="1" min="14" max="14"/>
-    <col width="60" customWidth="1" min="15" max="15"/>
-    <col width="60" customWidth="1" min="16" max="16"/>
-    <col width="60" customWidth="1" min="17" max="17"/>
-    <col width="45" customWidth="1" min="18" max="18"/>
-    <col width="45" customWidth="1" min="19" max="19"/>
-    <col width="60" customWidth="1" min="20" max="20"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="6" width="28" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="8" width="30" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="10" max="10" width="45" customWidth="1"/>
+    <col min="11" max="11" width="10" customWidth="1"/>
+    <col min="12" max="12" width="20" customWidth="1"/>
+    <col min="13" max="13" width="28" customWidth="1"/>
+    <col min="14" max="14" width="30" customWidth="1"/>
+    <col min="15" max="17" width="60" customWidth="1"/>
+    <col min="18" max="19" width="45" customWidth="1"/>
+    <col min="20" max="20" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Référence</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Langue</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Prix</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Nom</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Organisation</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Ville</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Courriel</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Téléphone</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Lien</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Âge</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Déposé par</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Nom proposant</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Courriel proposant</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Parcours</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Racines</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Audace</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Liens supplémentaires</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Références</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Documents</t>
-        </is>
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -560,52 +531,38 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="80" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="3" width="35" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="80" customWidth="1"/>
+    <col min="6" max="6" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Référence</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Nom</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Taille</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Chemin GitHub</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
